--- a/template/t5_ocr_report.xlsx
+++ b/template/t5_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="39">
   <si>
     <t>filename</t>
   </si>
@@ -40,18 +40,6 @@
     <t>black_radio</t>
   </si>
   <si>
-    <t>color_blue</t>
-  </si>
-  <si>
-    <t>color_green</t>
-  </si>
-  <si>
-    <t>color_yellow</t>
-  </si>
-  <si>
-    <t>color_red</t>
-  </si>
-  <si>
     <t>color_white</t>
   </si>
   <si>
@@ -64,6 +52,9 @@
     <t>green_centers</t>
   </si>
   <si>
+    <t>blue_centers</t>
+  </si>
+  <si>
     <t>micro_0015_XII.jpg</t>
   </si>
   <si>
@@ -137,9 +128,6 @@
   </si>
   <si>
     <t>color_detection</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>Yes</t>
@@ -474,10 +462,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -517,28 +505,19 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -553,192 +532,156 @@
         <v>22.6216814159292</v>
       </c>
       <c r="I2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+        <v>38</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>408</v>
+      </c>
+      <c r="H3">
+        <v>48.11320754716981</v>
+      </c>
+      <c r="I3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>410</v>
+      </c>
+      <c r="H4">
+        <v>42.39917269906929</v>
+      </c>
+      <c r="I4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>3563</v>
+      </c>
+      <c r="H5">
+        <v>20.44880624426079</v>
+      </c>
+      <c r="I5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
         <v>17</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B6" t="s">
         <v>29</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>410</v>
-      </c>
-      <c r="H3">
-        <v>48.34905660377358</v>
-      </c>
-      <c r="I3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>416</v>
-      </c>
-      <c r="H4">
-        <v>43.01964839710445</v>
-      </c>
-      <c r="I4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" t="s">
-        <v>42</v>
-      </c>
-      <c r="L4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>3826</v>
-      </c>
-      <c r="H5">
-        <v>21.95821854912764</v>
-      </c>
-      <c r="I5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>2</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
       </c>
       <c r="C6">
         <v>0.8459755182266235</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -753,42 +696,33 @@
         <v>37.22927557879014</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" t="s">
-        <v>42</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>38</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>0.993732750415802</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -803,42 +737,33 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K7" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
+        <v>38</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
         <v>2</v>
       </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>0.9968959093093872</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -853,42 +778,33 @@
         <v>37.26661687826736</v>
       </c>
       <c r="I8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" t="s">
-        <v>42</v>
-      </c>
-      <c r="K8" t="s">
-        <v>41</v>
-      </c>
-      <c r="L8" t="s">
-        <v>42</v>
-      </c>
-      <c r="M8" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>38</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>0.9980829358100891</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -903,42 +819,33 @@
         <v>34.12994772218073</v>
       </c>
       <c r="I9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" t="s">
-        <v>42</v>
-      </c>
-      <c r="K9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L9" t="s">
-        <v>42</v>
-      </c>
-      <c r="M9" t="s">
-        <v>42</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>38</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -953,42 +860,33 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" t="s">
-        <v>42</v>
-      </c>
-      <c r="K10" t="s">
-        <v>41</v>
-      </c>
-      <c r="L10" t="s">
-        <v>41</v>
-      </c>
-      <c r="M10" t="s">
-        <v>42</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <v>38</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>0.9044368863105774</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1003,98 +901,101 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>41</v>
-      </c>
-      <c r="J11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" t="s">
-        <v>41</v>
-      </c>
-      <c r="L11" t="s">
-        <v>41</v>
-      </c>
-      <c r="M11" t="s">
-        <v>42</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>38</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
       <c r="I12" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" t="s">
-        <v>41</v>
-      </c>
-      <c r="L12" t="s">
-        <v>41</v>
-      </c>
-      <c r="M12" t="s">
-        <v>42</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+        <v>38</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
       <c r="I13" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" t="s">
-        <v>41</v>
-      </c>
-      <c r="L13" t="s">
-        <v>41</v>
-      </c>
-      <c r="M13" t="s">
-        <v>42</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/template/t5_ocr_report.xlsx
+++ b/template/t5_ocr_report.xlsx
@@ -1,20 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView windowWidth="29400" windowHeight="10700"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="40">
   <si>
     <t>filename</t>
   </si>
@@ -55,106 +68,452 @@
     <t>blue_centers</t>
   </si>
   <si>
+    <t>white_centers</t>
+  </si>
+  <si>
     <t>micro_0015_XII.jpg</t>
   </si>
   <si>
+    <t>XⅡ</t>
+  </si>
+  <si>
+    <t>color_detection</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>micro_0019_X3.jpg</t>
   </si>
   <si>
+    <t>X3</t>
+  </si>
+  <si>
     <t>micro_0013_X1.jpg</t>
   </si>
   <si>
+    <t>X1</t>
+  </si>
+  <si>
     <t>micro_0004_X.jpg</t>
   </si>
   <si>
+    <t>X</t>
+  </si>
+  <si>
     <t>micro_0009_S.jpg</t>
   </si>
   <si>
+    <t>SⅡ</t>
+  </si>
+  <si>
     <t>micro_0003_SF.jpg</t>
   </si>
   <si>
+    <t>SF</t>
+  </si>
+  <si>
     <t>micro_0012_0S3.jpg</t>
   </si>
   <si>
+    <t>S3</t>
+  </si>
+  <si>
     <t>micro_0008_S1.jpg</t>
   </si>
   <si>
-    <t>micro_0014_FXII_K.jpg</t>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>micro_0010_FXII.jpg</t>
+  </si>
+  <si>
+    <t>FXⅡ</t>
   </si>
   <si>
     <t>micro_0011_XFS.jpg</t>
   </si>
   <si>
+    <t>FSⅡ</t>
+  </si>
+  <si>
     <t>micro_0018_D2.jpg</t>
   </si>
   <si>
+    <t>D2</t>
+  </si>
+  <si>
     <t>micro_0002_D1.jpg</t>
   </si>
   <si>
-    <t>XⅡ</t>
-  </si>
-  <si>
-    <t>X3</t>
-  </si>
-  <si>
-    <t>X1</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>SⅡ</t>
-  </si>
-  <si>
-    <t>SF</t>
-  </si>
-  <si>
-    <t>S3</t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>FXⅡ</t>
-  </si>
-  <si>
-    <t>FSⅡ</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
     <t>D1</t>
-  </si>
-  <si>
-    <t>color_detection</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -162,18 +521,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -456,16 +1109,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="3" max="3" width="12.9230769230769"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -505,34 +1161,37 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.807626724243164</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>409</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>22.6216814159292</v>
+        <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -546,34 +1205,37 @@
       <c r="M2">
         <v>0</v>
       </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.989889144897461</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>48.11320754716981</v>
+        <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -587,34 +1249,37 @@
       <c r="M3">
         <v>0</v>
       </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.988746345043182</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>42.39917269906929</v>
+        <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -628,34 +1293,37 @@
       <c r="M4">
         <v>0</v>
       </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5">
+        <v>0.949999332427979</v>
+      </c>
+      <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>3563</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>20.44880624426079</v>
+        <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -669,35 +1337,38 @@
       <c r="M5">
         <v>0</v>
       </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6">
+        <v>0.801347136497498</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6">
-        <v>0.8459755182266235</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>997</v>
-      </c>
-      <c r="H6">
-        <v>37.22927557879014</v>
-      </c>
-      <c r="I6" t="s">
-        <v>38</v>
-      </c>
       <c r="J6">
         <v>1</v>
       </c>
@@ -710,19 +1381,22 @@
       <c r="M6">
         <v>0</v>
       </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>0.993732750415802</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -737,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -751,224 +1425,242 @@
       <c r="M7">
         <v>0</v>
       </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8">
+        <v>0.994745969772339</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
         <v>31</v>
       </c>
-      <c r="C8">
-        <v>0.9968959093093872</v>
-      </c>
-      <c r="D8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>998</v>
-      </c>
-      <c r="H8">
-        <v>37.26661687826736</v>
-      </c>
-      <c r="I8" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
+      <c r="C9">
+        <v>0.9978928565979</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
         <v>32</v>
-      </c>
-      <c r="C9">
-        <v>0.9980829358100891</v>
-      </c>
-      <c r="D9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>914</v>
-      </c>
-      <c r="H9">
-        <v>34.12994772218073</v>
-      </c>
-      <c r="I9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" t="s">
-        <v>21</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0.93835175037384</v>
       </c>
       <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11">
+        <v>0.938299298286438</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
         <v>37</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
         <v>38</v>
       </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11">
-        <v>0.9044368863105774</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11" t="s">
-        <v>38</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12" t="s">
-        <v>38</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -983,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -995,10 +1687,14 @@
         <v>0</v>
       </c>
       <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/template/t5_ocr_report.xlsx
+++ b/template/t5_ocr_report.xlsx
@@ -1,28 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="10700"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -74,446 +61,103 @@
     <t>micro_0015_XII.jpg</t>
   </si>
   <si>
+    <t>micro_0019_X3.jpg</t>
+  </si>
+  <si>
+    <t>micro_0013_X1.jpg</t>
+  </si>
+  <si>
+    <t>micro_0004_X.jpg</t>
+  </si>
+  <si>
+    <t>micro_0009_S.jpg</t>
+  </si>
+  <si>
+    <t>micro_0003_SF.jpg</t>
+  </si>
+  <si>
+    <t>micro_0012_0S3.jpg</t>
+  </si>
+  <si>
+    <t>micro_0008_S1.jpg</t>
+  </si>
+  <si>
+    <t>micro_0014_FXII_K.jpg</t>
+  </si>
+  <si>
+    <t>micro_0011_XFS.jpg</t>
+  </si>
+  <si>
+    <t>micro_0018_D2.jpg</t>
+  </si>
+  <si>
+    <t>micro_0002_D1.jpg</t>
+  </si>
+  <si>
     <t>XⅡ</t>
   </si>
   <si>
+    <t>X3</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>SⅡ</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>FXⅡ</t>
+  </si>
+  <si>
+    <t>FSⅡ</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
     <t>color_detection</t>
   </si>
   <si>
     <t>Yes</t>
-  </si>
-  <si>
-    <t>micro_0019_X3.jpg</t>
-  </si>
-  <si>
-    <t>X3</t>
-  </si>
-  <si>
-    <t>micro_0013_X1.jpg</t>
-  </si>
-  <si>
-    <t>X1</t>
-  </si>
-  <si>
-    <t>micro_0004_X.jpg</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>micro_0009_S.jpg</t>
-  </si>
-  <si>
-    <t>SⅡ</t>
-  </si>
-  <si>
-    <t>micro_0003_SF.jpg</t>
-  </si>
-  <si>
-    <t>SF</t>
-  </si>
-  <si>
-    <t>micro_0012_0S3.jpg</t>
-  </si>
-  <si>
-    <t>S3</t>
-  </si>
-  <si>
-    <t>micro_0008_S1.jpg</t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>micro_0010_FXII.jpg</t>
-  </si>
-  <si>
-    <t>FXⅡ</t>
-  </si>
-  <si>
-    <t>micro_0011_XFS.jpg</t>
-  </si>
-  <si>
-    <t>FSⅡ</t>
-  </si>
-  <si>
-    <t>micro_0018_D2.jpg</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>micro_0002_D1.jpg</t>
-  </si>
-  <si>
-    <t>D1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -521,312 +165,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1109,17 +459,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
-  <cols>
-    <col min="3" max="3" width="12.9230769230769"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
@@ -1170,13 +517,13 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C2">
-        <v>0.807626724243164</v>
+        <v>0.8076267242431641</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1191,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1211,16 +558,16 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C3">
-        <v>0.989889144897461</v>
+        <v>0.9898891448974609</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1235,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1255,16 +602,16 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C4">
-        <v>0.988746345043182</v>
+        <v>0.9887463450431824</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1279,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1299,16 +646,16 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C5">
-        <v>0.949999332427979</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1323,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1343,16 +690,16 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C6">
-        <v>0.801347136497498</v>
+        <v>0.7977324724197388</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1367,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1387,16 +734,16 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C7">
-        <v>0.993732750415802</v>
+        <v>0.9948632717132568</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1411,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1431,16 +778,16 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>0.994745969772339</v>
+        <v>0.9970926642417908</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1455,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1475,16 +822,16 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9">
-        <v>0.9978928565979</v>
+        <v>0.9978928565979004</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1499,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1519,16 +866,16 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10">
-        <v>0.93835175037384</v>
+        <v>0.9579722285270691</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1543,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1563,16 +910,16 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
         <v>35</v>
       </c>
       <c r="C11">
-        <v>0.938299298286438</v>
+        <v>0.9292575716972351</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1587,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1607,16 +954,16 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
         <v>36</v>
       </c>
-      <c r="B12" t="s">
-        <v>37</v>
-      </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1631,16 +978,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12">
         <v>1</v>
@@ -1651,16 +998,16 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1675,7 +1022,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1695,6 +1042,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/template/t5_ocr_report.xlsx
+++ b/template/t5_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
   <si>
     <t>filename</t>
   </si>
@@ -56,6 +56,12 @@
   </si>
   <si>
     <t>white_centers</t>
+  </si>
+  <si>
+    <t>is_tri</t>
+  </si>
+  <si>
+    <t>is_double</t>
   </si>
   <si>
     <t>micro_0015_XII.jpg</t>
@@ -465,10 +471,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -511,19 +517,25 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C2">
         <v>0.8076267242431641</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -538,7 +550,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -555,19 +567,25 @@
       <c r="N2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>0.9898891448974609</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -582,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -599,19 +617,25 @@
       <c r="N3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>0.9887463450431824</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -626,7 +650,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -643,19 +667,25 @@
       <c r="N4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -670,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -687,19 +717,25 @@
       <c r="N5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>0.7977324724197388</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -714,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -731,19 +767,25 @@
       <c r="N6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>0.9948632717132568</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -758,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -775,19 +817,25 @@
       <c r="N7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>0.9970926642417908</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -802,7 +850,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -819,19 +867,25 @@
       <c r="N8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>0.9978928565979004</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -846,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -863,19 +917,25 @@
       <c r="N9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C10">
         <v>0.9579722285270691</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -890,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -907,107 +967,125 @@
       <c r="N10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>0.9292575716972351</v>
       </c>
       <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
         <v>38</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
         <v>39</v>
       </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="s">
-        <v>37</v>
-      </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1022,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1038,6 +1116,12 @@
       </c>
       <c r="N13">
         <v>1</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
